--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.35306289323048</v>
+        <v>5.419872720149953</v>
       </c>
       <c r="D2" t="n">
-        <v>34.71190304728729</v>
+        <v>5.640684245184185</v>
       </c>
       <c r="E2" t="n">
-        <v>14.5190280262705</v>
+        <v>2.359342054268957</v>
       </c>
       <c r="F2" t="n">
-        <v>13.56151149606035</v>
+        <v>2.203745618109808</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.79245253962867</v>
+        <v>4.841273537689659</v>
       </c>
       <c r="D3" t="n">
-        <v>30.90425865383757</v>
+        <v>5.021942031248606</v>
       </c>
       <c r="E3" t="n">
-        <v>14.5190280262705</v>
+        <v>2.359342054268957</v>
       </c>
       <c r="F3" t="n">
-        <v>13.56151149606035</v>
+        <v>2.203745618109808</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.70054126481186</v>
+        <v>5.151337955531927</v>
       </c>
       <c r="D4" t="n">
-        <v>32.47174789792624</v>
+        <v>5.276659033413015</v>
       </c>
       <c r="E4" t="n">
-        <v>14.5190280262705</v>
+        <v>2.359342054268957</v>
       </c>
       <c r="F4" t="n">
-        <v>13.56151149606035</v>
+        <v>2.203745618109808</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.54863099301687</v>
+        <v>10.16415253636524</v>
       </c>
       <c r="D5" t="n">
-        <v>61.60609957647233</v>
+        <v>10.01099118117675</v>
       </c>
       <c r="E5" t="n">
-        <v>14.5190280262705</v>
+        <v>2.359342054268957</v>
       </c>
       <c r="F5" t="n">
-        <v>13.56151149606035</v>
+        <v>2.203745618109808</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.25356223155457</v>
+        <v>10.60370386262762</v>
       </c>
       <c r="D6" t="n">
-        <v>64.05345436345458</v>
+        <v>10.40868633406137</v>
       </c>
       <c r="E6" t="n">
-        <v>14.5190280262705</v>
+        <v>2.359342054268957</v>
       </c>
       <c r="F6" t="n">
-        <v>13.56151149606035</v>
+        <v>2.203745618109808</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.7100303578955</v>
+        <v>7.59037993315802</v>
       </c>
       <c r="D7" t="n">
-        <v>46.80259878410875</v>
+        <v>7.605422302417671</v>
       </c>
       <c r="E7" t="n">
-        <v>14.5190280262705</v>
+        <v>2.359342054268957</v>
       </c>
       <c r="F7" t="n">
-        <v>13.56151149606035</v>
+        <v>2.203745618109808</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
